--- a/public/templates-files/roofing-estimate-template.xlsx
+++ b/public/templates-files/roofing-estimate-template.xlsx
@@ -10,14 +10,14 @@
     <sheet sheetId="4" name="How to Use" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Estimate'!$A1:$G74</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Estimate'!$A1:$G82</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="159">
   <si>
     <t>Roofing Estimate</t>
   </si>
@@ -193,7 +193,10 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>Free template by BuildWorkPro — buildworkpro.com/templates. Based on measurements taken before tear-off. Hidden damage and owner-requested changes are priced by written change order first. Check your state’s home-improvement contract and deposit rules. Not legal advice.</t>
+    <t>Based on pre-tear-off measurements. Hidden damage and owner changes are priced by written change order first. Check your state’s home-improvement contract rules. Not legal advice.</t>
+  </si>
+  <si>
+    <t>Free template by BuildWorkPro — buildworkpro.com/templates.</t>
   </si>
   <si>
     <t>Roof Takeoff</t>
@@ -508,7 +511,7 @@
     <numFmt numFmtId="171" formatCode="#,##0;-#,##0;&quot;&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0"/>
     <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="0.00;-0.00;&quot;&quot;"/>
+    <numFmt numFmtId="174" formatCode="0.0##;-0.0##;&quot;&quot;"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -831,6 +834,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -875,9 +881,6 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1240,7 +1243,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1522,56 +1525,56 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="16">
+        <v>5</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="21">
+        <f>IF(OR(C31="",E31=""),"",C31*E31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="16">
+        <v>6</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="21">
+        <f>IF(OR(C32="",E32=""),"",C32*E32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B33" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="24">
-        <f>SUM(G27:G30)</f>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="24">
+        <f>SUM(G27:G32)</f>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>5</v>
-      </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="21">
-        <f>IF(OR(C34="",E34=""),"",C34*E34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="16">
-        <v>6</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="21">
-        <f>IF(OR(C35="",E35=""),"",C35*E35)</f>
-      </c>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
@@ -1613,34 +1616,47 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="24">
-        <f>SUM(G34:G38)</f>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="A39" s="16">
+        <v>10</v>
+      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="21">
+        <f>IF(OR(C39="",E39=""),"",C39*E39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>11</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="21">
+        <f>IF(OR(C40="",E40=""),"",C40*E40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="16">
+        <v>12</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="21">
+        <f>IF(OR(C41="",E41=""),"",C41*E41)</f>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="18"/>
@@ -1652,284 +1668,360 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="16">
-        <v>11</v>
-      </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="21">
-        <f>IF(OR(C43="",E43=""),"",C43*E43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="16">
-        <v>12</v>
-      </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="21">
-        <f>IF(OR(C44="",E44=""),"",C44*E44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="16">
-        <v>13</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="21">
-        <f>IF(OR(C45="",E45=""),"",C45*E45)</f>
-      </c>
+      <c r="A43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="24">
+        <f>SUM(G36:G42)</f>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="16">
+        <v>14</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="21">
+        <f>IF(OR(C46="",E46=""),"",C46*E46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="16">
+        <v>15</v>
+      </c>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="21">
+        <f>IF(OR(C47="",E47=""),"",C47*E47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="16">
+        <v>16</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="21">
+        <f>IF(OR(C48="",E48=""),"",C48*E48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="16">
+        <v>17</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="21">
+        <f>IF(OR(C49="",E49=""),"",C49*E49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="16">
+        <v>18</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="21">
+        <f>IF(OR(C50="",E50=""),"",C50*E50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="16">
+        <v>19</v>
+      </c>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="21">
+        <f>IF(OR(C51="",E51=""),"",C51*E51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B52" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="24">
-        <f>SUM(G42:G45)</f>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="25" t="s">
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="24">
+        <f>SUM(G46:G51)</f>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B54" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="26">
-        <f>G31+G39+G46</f>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="27" t="s">
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="26">
+        <f>G33+G43+G52</f>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="G49" s="28">
-        <f>SUMIF(F27:F30,"Y",G27:G30)+SUMIF(F34:F38,"Y",G34:G38)+SUMIF(F42:F45,"Y",G42:G45)</f>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="27" t="s">
+      <c r="G55" s="28">
+        <f>SUMIF(F27:F32,"Y",G27:G32)+SUMIF(F36:F42,"Y",G36:G42)+SUMIF(F46:F51,"Y",G46:G51)</f>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="29">
+      <c r="E56" s="29">
         <v>0</v>
       </c>
-      <c r="G50" s="30">
-        <f>ROUND(G49*E50,2)</f>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="25" t="s">
+      <c r="G56" s="30">
+        <f>ROUND(G55*E56,2)</f>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B57" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="31">
-        <f>G48+G50</f>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="27" t="s">
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="31">
+        <f>G54+G56</f>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E58" s="32">
         <v>0.3</v>
       </c>
-      <c r="G52" s="30">
-        <f>ROUND(G51*E52,2)</f>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="27" t="s">
+      <c r="G58" s="30">
+        <f>ROUND(G57*E58,2)</f>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="G53" s="30">
-        <f>G51-G52</f>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
+      <c r="G59" s="30">
+        <f>G57-G58</f>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B61" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C61" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D61" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E61" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F55" s="13" t="s">
+      <c r="F61" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G61" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="20"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="20"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="20"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="20"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="20"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="20"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-    </row>
-    <row r="62" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-    </row>
-    <row r="63" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="33" t="s">
+    <row r="67" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+    </row>
+    <row r="69" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="E65" s="33" t="s">
+      <c r="E71" s="33" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="67" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="34"/>
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="35" t="s">
+    <row r="73" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="34"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="E68" s="35" t="s">
+      <c r="E74" s="35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="34"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="35" t="s">
+    <row r="75" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="34"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="34"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E70" s="35" t="s">
+      <c r="E76" s="35" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="71" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="34"/>
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="35" t="s">
+    <row r="77" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="34"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E78" s="35" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="74" ht="39" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="36" t="s">
+    <row r="80" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
+      <c r="B80" s="36"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+    </row>
+    <row r="82" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:G7"/>
@@ -1948,31 +2040,32 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="A22:G23"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="A61:G63"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="E67:G67"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="A67:G69"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A82:G82"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F27:F30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F27:F32">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F34:F38">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F36:F42">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F42:F45">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from the list" error="Choose one of: Y, N" sqref="F46:F51">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A74" r:id="rId1"/>
+    <hyperlink ref="A82" r:id="rId1"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -1999,12 +2092,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2023,204 +2116,204 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="38">
+      <c r="A7" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="39">
         <v>52</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="39">
         <v>18</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="40">
         <v>6</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <f>IF(B7="","",SQRT(1+(N(D7)/12)^2))</f>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="42">
         <f>IF(OR(B7="",C7=""),"",B7*C7*E7)</f>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="38">
+      <c r="A8" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="39">
         <v>52</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="39">
         <v>18</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="40">
         <v>6</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="41">
         <f>IF(B8="","",SQRT(1+(N(D8)/12)^2))</f>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="42">
         <f>IF(OR(B8="",C8=""),"",B8*C8*E8)</f>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="38">
+      <c r="A9" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="39">
         <v>26</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="39">
         <v>12</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="40">
         <v>8</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="41">
         <f>IF(B9="","",SQRT(1+(N(D9)/12)^2))</f>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <f>IF(OR(B9="",C9=""),"",B9*C9*E9)</f>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="38">
+      <c r="A10" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="39">
         <v>26</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="39">
         <v>12</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="40">
         <v>8</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="41">
         <f>IF(B10="","",SQRT(1+(N(D10)/12)^2))</f>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="42">
         <f>IF(OR(B10="",C10=""),"",B10*C10*E10)</f>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="40">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41">
         <f>IF(B11="","",SQRT(1+(N(D11)/12)^2))</f>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="42">
         <f>IF(OR(B11="",C11=""),"",B11*C11*E11)</f>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40">
+      <c r="A12" s="38"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41">
         <f>IF(B12="","",SQRT(1+(N(D12)/12)^2))</f>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="42">
         <f>IF(OR(B12="",C12=""),"",B12*C12*E12)</f>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41">
         <f>IF(B13="","",SQRT(1+(N(D13)/12)^2))</f>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <f>IF(OR(B13="",C13=""),"",B13*C13*E13)</f>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40">
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41">
         <f>IF(B14="","",SQRT(1+(N(D14)/12)^2))</f>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <f>IF(OR(B14="",C14=""),"",B14*C14*E14)</f>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41">
         <f>IF(B15="","",SQRT(1+(N(D15)/12)^2))</f>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="42">
         <f>IF(OR(B15="",C15=""),"",B15*C15*E15)</f>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40">
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41">
         <f>IF(B16="","",SQRT(1+(N(D16)/12)^2))</f>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="42">
         <f>IF(OR(B16="",C16=""),"",B16*C16*E16)</f>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
-      <c r="F17" s="42">
+      <c r="F17" s="43">
         <f>SUM(F7:F16)</f>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="44">
+      <c r="A18" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="45">
         <f>F17/100</f>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2232,180 +2325,180 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="45">
+      <c r="F22" s="46">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
-      <c r="F23" s="45">
+      <c r="F23" s="46">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="46">
+      <c r="F24" s="47">
         <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="45">
+      <c r="F25" s="46">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="46">
+      <c r="F26" s="47">
         <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
-      <c r="F27" s="45">
+      <c r="F27" s="46">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
-      <c r="F28" s="46">
+      <c r="F28" s="47">
         <v>1000</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
-      <c r="F29" s="47">
+      <c r="F29" s="48">
         <v>5.625</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="46">
+      <c r="F32" s="47">
         <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="46">
+      <c r="F33" s="47">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="46">
+      <c r="F34" s="47">
         <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
-      <c r="F35" s="46">
+      <c r="F35" s="47">
         <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="46">
+      <c r="F36" s="47">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
-      <c r="F37" s="46">
+      <c r="F37" s="47">
         <v>22</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>34</v>
@@ -2420,210 +2513,210 @@
         <v>29</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="49" t="s">
+      <c r="A40" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="F40" s="44">
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="49"/>
+      <c r="E40" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="45">
         <f>F18</f>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="45">
+        <f>ROUND(F18*F23*F24/2000,1)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="48"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" s="44">
-        <f>ROUND(F18*F23*F24/2000,1)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="B42" s="48"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="44">
+      <c r="F42" s="45">
         <f>ROUNDUP(F18*(1+F21),1)</f>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="49" t="s">
+      <c r="A43" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="F43" s="50">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="F43" s="51">
         <f>ROUNDUP(F18*(1+F21)*F22,0)</f>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="51">
+        <f>ROUNDUP(F17/F28,0)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" s="51">
+        <f>ROUNDUP((F32*3*F27+F36*3)/F26,0)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="F46" s="51">
+        <f>F32+F33</f>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" s="51">
+        <f>ROUNDUP((F32+F33)/10,0)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" s="51">
+        <f>F34+F35</f>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="48"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="F44" s="50">
-        <f>ROUNDUP(F17/F28,0)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="F45" s="50">
-        <f>ROUNDUP((F32*3*F27+F36*3)/F26,0)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="48"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="50">
-        <f>F32+F33</f>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="48" t="s">
+      <c r="F49" s="51">
+        <f>ROUNDUP((F34+F35)/F25,0)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="F47" s="50">
-        <f>ROUNDUP((F32+F33)/10,0)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="48" t="s">
+      <c r="F50" s="51">
+        <f>F34</f>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="48"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="F48" s="50">
-        <f>F34+F35</f>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="F49" s="50">
-        <f>ROUNDUP((F34+F35)/F25,0)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="48"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="50">
-        <f>F34</f>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="50">
+      <c r="F51" s="51">
         <f>ROUNDUP(F37*12/F29,0)</f>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B52" s="48"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="49" t="s">
+      <c r="A52" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="F52" s="50">
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="51">
         <f>ROUNDUP(F17/32*1.05,0)</f>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
+      <c r="A54" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
     </row>
     <row r="56" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
+      <c r="A56" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -2689,12 +2782,12 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" ht="6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2715,7 +2808,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2725,7 +2818,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2735,7 +2828,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2745,36 +2838,36 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="20">
         <v>0</v>
@@ -2797,10 +2890,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="20">
         <v>190</v>
@@ -2823,10 +2916,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="20">
         <v>14</v>
@@ -2849,10 +2942,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="20">
         <v>95</v>
@@ -2875,10 +2968,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="20">
         <v>1.35</v>
@@ -2901,10 +2994,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="20">
         <v>3.2</v>
@@ -2927,10 +3020,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="20">
         <v>18</v>
@@ -2953,10 +3046,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" s="20">
         <v>24</v>
@@ -3074,40 +3167,40 @@
       </c>
     </row>
     <row r="26" ht="44" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
+      <c r="A26" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
     </row>
     <row r="28" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
+      <c r="A28" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
     </row>
     <row r="30" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
+      <c r="A30" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3145,7 +3238,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" ht="6" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3154,105 +3247,105 @@
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="54" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="54" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="54" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B15" s="57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="B17" s="51"/>
+      <c r="A17" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="36"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" ht="78" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="B20" s="36"/>
+      <c r="A20" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="2">
